--- a/artfynd/A 42950-2022 artfynd.xlsx
+++ b/artfynd/A 42950-2022 artfynd.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 42950-2022 artfynd.xlsx
+++ b/artfynd/A 42950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667418</v>
+        <v>124667414</v>
       </c>
       <c r="B2" t="n">
-        <v>56856</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720901</v>
+        <v>720926</v>
       </c>
       <c r="R2" t="n">
-        <v>7205865</v>
+        <v>7205896</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -779,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667414</v>
+        <v>124667418</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>56856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +793,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720926</v>
+        <v>720901</v>
       </c>
       <c r="R3" t="n">
-        <v>7205896</v>
+        <v>7205865</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 42950-2022 artfynd.xlsx
+++ b/artfynd/A 42950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667414</v>
+        <v>124667418</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>56856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720926</v>
+        <v>720901</v>
       </c>
       <c r="R2" t="n">
-        <v>7205896</v>
+        <v>7205865</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -770,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667418</v>
+        <v>124667414</v>
       </c>
       <c r="B3" t="n">
-        <v>56856</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720901</v>
+        <v>720926</v>
       </c>
       <c r="R3" t="n">
-        <v>7205865</v>
+        <v>7205896</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 42950-2022 artfynd.xlsx
+++ b/artfynd/A 42950-2022 artfynd.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 42950-2022 artfynd.xlsx
+++ b/artfynd/A 42950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667418</v>
+        <v>124667414</v>
       </c>
       <c r="B2" t="n">
-        <v>56856</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720901</v>
+        <v>720926</v>
       </c>
       <c r="R2" t="n">
-        <v>7205865</v>
+        <v>7205896</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667414</v>
+        <v>124667418</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>56856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +793,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720926</v>
+        <v>720901</v>
       </c>
       <c r="R3" t="n">
-        <v>7205896</v>
+        <v>7205865</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 42950-2022 artfynd.xlsx
+++ b/artfynd/A 42950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667414</v>
+        <v>124667418</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>56856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720926</v>
+        <v>720901</v>
       </c>
       <c r="R2" t="n">
-        <v>7205896</v>
+        <v>7205865</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667418</v>
+        <v>124667414</v>
       </c>
       <c r="B3" t="n">
-        <v>56856</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720901</v>
+        <v>720926</v>
       </c>
       <c r="R3" t="n">
-        <v>7205865</v>
+        <v>7205896</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 42950-2022 artfynd.xlsx
+++ b/artfynd/A 42950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667418</v>
+        <v>124667414</v>
       </c>
       <c r="B2" t="n">
-        <v>56856</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720901</v>
+        <v>720926</v>
       </c>
       <c r="R2" t="n">
-        <v>7205865</v>
+        <v>7205896</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667414</v>
+        <v>124667418</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>56856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +793,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720926</v>
+        <v>720901</v>
       </c>
       <c r="R3" t="n">
-        <v>7205896</v>
+        <v>7205865</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 42950-2022 artfynd.xlsx
+++ b/artfynd/A 42950-2022 artfynd.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 42950-2022 artfynd.xlsx
+++ b/artfynd/A 42950-2022 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 42950-2022 artfynd.xlsx
+++ b/artfynd/A 42950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667414</v>
+        <v>124667418</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>56856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720926</v>
+        <v>720901</v>
       </c>
       <c r="R2" t="n">
-        <v>7205896</v>
+        <v>7205865</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -770,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667418</v>
+        <v>124667414</v>
       </c>
       <c r="B3" t="n">
-        <v>56856</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720901</v>
+        <v>720926</v>
       </c>
       <c r="R3" t="n">
-        <v>7205865</v>
+        <v>7205896</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 42950-2022 artfynd.xlsx
+++ b/artfynd/A 42950-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667414</v>
+        <v>124667418</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>56949</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720926</v>
+        <v>720901</v>
       </c>
       <c r="R2" t="n">
-        <v>7205896</v>
+        <v>7205865</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667418</v>
+        <v>124667414</v>
       </c>
       <c r="B3" t="n">
-        <v>56856</v>
+        <v>80028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvasmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720901</v>
+        <v>720926</v>
       </c>
       <c r="R3" t="n">
-        <v>7205865</v>
+        <v>7205896</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
